--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6726D07-2D03-4A10-AC9B-47E1BEB4C507}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69870301-F5CB-4423-8EA8-D0CBC2E4375E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -210,6 +210,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1529,7 +1533,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="17">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="D8" s="18">
         <f>AVERAGE('Lịch sử giá'!F8:F37)</f>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69870301-F5CB-4423-8EA8-D0CBC2E4375E}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F12BCEE9-4D5B-4AF4-8DC2-6F2AD0E03153}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
     <sheet name="Giá trung bình (30 ngày)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lịch sử giá'!$C$1:$F$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lịch sử giá'!$D$1:$G$30</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1000" iterateDelta="0.01"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -54,19 +54,22 @@
     <t>Giá trung bình (30 ngày giao dịch gần nhất)</t>
   </si>
   <si>
-    <t>Mở cửa</t>
+    <t>Mã CP</t>
   </si>
   <si>
-    <t>Cao nhất</t>
+    <t>Giá mở cửa</t>
   </si>
   <si>
-    <t>Thấp nhất</t>
+    <t>Giá cao nhất</t>
   </si>
   <si>
-    <t>Đóng cửa</t>
+    <t>Giá thấp nhất</t>
   </si>
   <si>
-    <t>KL</t>
+    <t>Giá đóng cửa</t>
+  </si>
+  <si>
+    <t>Khối lượng GD</t>
   </si>
 </sst>
 </file>
@@ -161,9 +164,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -174,7 +174,6 @@
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -195,6 +194,12 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,873 +538,1011 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="13.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" style="20" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H1" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4">
         <v>46113</v>
       </c>
-      <c r="C2" s="3">
+      <c r="D2" s="20">
         <v>41.1</v>
       </c>
-      <c r="D2" s="3">
+      <c r="E2" s="20">
         <v>41.85</v>
       </c>
-      <c r="E2" s="3">
+      <c r="F2" s="20">
         <v>40.5</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G2" s="21">
         <v>40.700000000000003</v>
       </c>
-      <c r="G2" s="21">
+      <c r="H2" s="19">
         <v>4263100</v>
       </c>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4">
         <v>46114</v>
       </c>
-      <c r="C3" s="3">
+      <c r="D3" s="20">
         <v>41</v>
       </c>
-      <c r="D3" s="3">
+      <c r="E3" s="20">
         <v>41.45</v>
       </c>
-      <c r="E3" s="3">
+      <c r="F3" s="20">
         <v>40.049999999999997</v>
       </c>
-      <c r="F3" s="6">
+      <c r="G3" s="21">
         <v>40.4</v>
       </c>
-      <c r="G3" s="21">
+      <c r="H3" s="19">
         <v>2560600</v>
       </c>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
         <v>46115</v>
       </c>
-      <c r="C4" s="3">
+      <c r="D4" s="20">
         <v>40.9</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E4" s="20">
         <v>41.35</v>
       </c>
-      <c r="E4" s="3">
+      <c r="F4" s="20">
         <v>40.200000000000003</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="21">
         <v>40.200000000000003</v>
       </c>
-      <c r="G4" s="21">
+      <c r="H4" s="19">
         <v>2933800</v>
       </c>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4">
         <v>46118</v>
       </c>
-      <c r="C5" s="3">
+      <c r="D5" s="20">
         <v>40.200000000000003</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E5" s="20">
         <v>40.200000000000003</v>
       </c>
-      <c r="E5" s="3">
+      <c r="F5" s="20">
         <v>38.9</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="21">
         <v>38.9</v>
       </c>
-      <c r="G5" s="21">
+      <c r="H5" s="19">
         <v>3124000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4">
         <v>46119</v>
       </c>
-      <c r="C6" s="3">
+      <c r="D6" s="20">
         <v>38.950000000000003</v>
       </c>
-      <c r="D6" s="3">
+      <c r="E6" s="20">
         <v>39.549999999999997</v>
       </c>
-      <c r="E6" s="3">
+      <c r="F6" s="20">
         <v>38.549999999999997</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="21">
         <v>38.6</v>
       </c>
-      <c r="G6" s="21">
+      <c r="H6" s="19">
         <v>1984000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4">
         <v>46120</v>
       </c>
-      <c r="C7" s="3">
+      <c r="D7" s="20">
         <v>39.5</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E7" s="20">
         <v>40.75</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="20">
         <v>38.950000000000003</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="21">
         <v>40.5</v>
       </c>
-      <c r="G7" s="21">
+      <c r="H7" s="19">
         <v>3490600</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4">
         <v>46121</v>
       </c>
-      <c r="C8" s="3">
+      <c r="D8" s="20">
         <v>40.5</v>
       </c>
-      <c r="D8" s="3">
+      <c r="E8" s="20">
         <v>40.5</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="20">
         <v>39.5</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="21">
         <v>39.5</v>
       </c>
-      <c r="G8" s="21">
+      <c r="H8" s="19">
         <v>2983000</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4">
         <v>46122</v>
       </c>
-      <c r="C9" s="3">
+      <c r="D9" s="20">
         <v>39.950000000000003</v>
       </c>
-      <c r="D9" s="3">
+      <c r="E9" s="20">
         <v>42</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="20">
         <v>39.549999999999997</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="21">
         <v>41.15</v>
       </c>
-      <c r="G9" s="21">
+      <c r="H9" s="19">
         <v>5697200</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4">
         <v>46125</v>
       </c>
-      <c r="C10" s="3">
+      <c r="D10" s="20">
         <v>41.9</v>
       </c>
-      <c r="D10" s="3">
+      <c r="E10" s="20">
         <v>41.95</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="20">
         <v>40.5</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="21">
         <v>40.700000000000003</v>
       </c>
-      <c r="G10" s="21">
+      <c r="H10" s="19">
         <v>3019000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
         <v>46126</v>
       </c>
-      <c r="C11" s="3">
+      <c r="D11" s="20">
         <v>41.2</v>
       </c>
-      <c r="D11" s="3">
+      <c r="E11" s="20">
         <v>41.2</v>
       </c>
-      <c r="E11" s="3">
+      <c r="F11" s="20">
         <v>40.1</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="21">
         <v>40.15</v>
       </c>
-      <c r="G11" s="21">
+      <c r="H11" s="19">
         <v>2218200</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4">
         <v>46127</v>
       </c>
-      <c r="C12" s="3">
+      <c r="D12" s="20">
         <v>40.15</v>
       </c>
-      <c r="D12" s="3">
+      <c r="E12" s="20">
         <v>40.700000000000003</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="20">
         <v>39.65</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="21">
         <v>39.799999999999997</v>
       </c>
-      <c r="G12" s="21">
+      <c r="H12" s="19">
         <v>2864800</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4">
         <v>46128</v>
       </c>
-      <c r="C13" s="3">
+      <c r="D13" s="20">
         <v>40.1</v>
       </c>
-      <c r="D13" s="3">
+      <c r="E13" s="20">
         <v>40.1</v>
       </c>
-      <c r="E13" s="3">
+      <c r="F13" s="20">
         <v>38.9</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G13" s="21">
         <v>39.1</v>
       </c>
-      <c r="G13" s="21">
+      <c r="H13" s="19">
         <v>3333400</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="4">
         <v>46129</v>
       </c>
-      <c r="C14" s="3">
+      <c r="D14" s="20">
         <v>39.4</v>
       </c>
-      <c r="D14" s="3">
+      <c r="E14" s="20">
         <v>40.450000000000003</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="20">
         <v>38.950000000000003</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="21">
         <v>39.950000000000003</v>
       </c>
-      <c r="G14" s="21">
+      <c r="H14" s="19">
         <v>2901300</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4">
         <v>46132</v>
       </c>
-      <c r="C15" s="3">
+      <c r="D15" s="20">
         <v>40.1</v>
       </c>
-      <c r="D15" s="3">
+      <c r="E15" s="20">
         <v>40.299999999999997</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="20">
         <v>39.299999999999997</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="21">
         <v>39.450000000000003</v>
       </c>
-      <c r="G15" s="21">
+      <c r="H15" s="19">
         <v>1765400</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="4">
         <v>46133</v>
       </c>
-      <c r="C16" s="3">
+      <c r="D16" s="20">
         <v>39.450000000000003</v>
       </c>
-      <c r="D16" s="3">
+      <c r="E16" s="20">
         <v>40</v>
       </c>
-      <c r="E16" s="3">
+      <c r="F16" s="20">
         <v>39.299999999999997</v>
       </c>
-      <c r="F16" s="6">
+      <c r="G16" s="21">
         <v>39.35</v>
       </c>
-      <c r="G16" s="21">
+      <c r="H16" s="19">
         <v>1986400</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4">
         <v>46134</v>
       </c>
-      <c r="C17" s="3">
+      <c r="D17" s="20">
         <v>39.6</v>
       </c>
-      <c r="D17" s="3">
+      <c r="E17" s="20">
         <v>39.6</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="20">
         <v>39</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="21">
         <v>39</v>
       </c>
-      <c r="G17" s="21">
+      <c r="H17" s="19">
         <v>1910900</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="4">
         <v>46135</v>
       </c>
-      <c r="C18" s="3">
+      <c r="D18" s="20">
         <v>39.1</v>
       </c>
-      <c r="D18" s="3">
+      <c r="E18" s="20">
         <v>39.700000000000003</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="20">
         <v>38</v>
       </c>
-      <c r="F18" s="6">
+      <c r="G18" s="21">
         <v>39.299999999999997</v>
       </c>
-      <c r="G18" s="21">
+      <c r="H18" s="19">
         <v>3786500</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4">
         <v>46136</v>
       </c>
-      <c r="C19" s="3">
+      <c r="D19" s="20">
         <v>39.65</v>
       </c>
-      <c r="D19" s="3">
+      <c r="E19" s="20">
         <v>41.35</v>
       </c>
-      <c r="E19" s="3">
+      <c r="F19" s="20">
         <v>39.549999999999997</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G19" s="21">
         <v>39.700000000000003</v>
       </c>
-      <c r="G19" s="21">
+      <c r="H19" s="19">
         <v>6401800</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="4">
         <v>46140</v>
       </c>
-      <c r="C20" s="3">
+      <c r="D20" s="20">
         <v>38.200000000000003</v>
       </c>
-      <c r="D20" s="3">
+      <c r="E20" s="20">
         <v>39.200000000000003</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="20">
         <v>36.950000000000003</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G20" s="21">
         <v>36.950000000000003</v>
       </c>
-      <c r="G20" s="21">
+      <c r="H20" s="19">
         <v>6503400</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="4">
         <v>46141</v>
       </c>
-      <c r="C21" s="3">
+      <c r="D21" s="20">
         <v>37</v>
       </c>
-      <c r="D21" s="3">
+      <c r="E21" s="20">
         <v>37.450000000000003</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="20">
         <v>36.25</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G21" s="21">
         <v>37.15</v>
       </c>
-      <c r="G21" s="21">
+      <c r="H21" s="19">
         <v>3564100</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="4">
         <v>46146</v>
       </c>
-      <c r="C22" s="3">
+      <c r="D22" s="20">
         <v>38.5</v>
       </c>
-      <c r="D22" s="3">
+      <c r="E22" s="20">
         <v>39.75</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="20">
         <v>38.1</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="21">
         <v>38.700000000000003</v>
       </c>
-      <c r="G22" s="21">
+      <c r="H22" s="19">
         <v>4403600</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="4">
         <v>46147</v>
       </c>
-      <c r="C23" s="3">
+      <c r="D23" s="20">
         <v>38.65</v>
       </c>
-      <c r="D23" s="3">
+      <c r="E23" s="20">
         <v>39.700000000000003</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="20">
         <v>37.799999999999997</v>
       </c>
-      <c r="F23" s="6">
+      <c r="G23" s="21">
         <v>39.25</v>
       </c>
-      <c r="G23" s="21">
+      <c r="H23" s="19">
         <v>3878000</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4">
         <v>46148</v>
       </c>
-      <c r="C24" s="3">
+      <c r="D24" s="20">
         <v>39.25</v>
       </c>
-      <c r="D24" s="3">
+      <c r="E24" s="20">
         <v>39.6</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="20">
         <v>38.65</v>
       </c>
-      <c r="F24" s="6">
+      <c r="G24" s="21">
         <v>39</v>
       </c>
-      <c r="G24" s="21">
+      <c r="H24" s="19">
         <v>3098200</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4">
         <v>46149</v>
       </c>
-      <c r="C25" s="3">
+      <c r="D25" s="20">
         <v>38.9</v>
       </c>
-      <c r="D25" s="3">
+      <c r="E25" s="20">
         <v>38.9</v>
       </c>
-      <c r="E25" s="3">
+      <c r="F25" s="20">
         <v>37.700000000000003</v>
       </c>
-      <c r="F25" s="6">
+      <c r="G25" s="21">
         <v>37.700000000000003</v>
       </c>
-      <c r="G25" s="21">
+      <c r="H25" s="19">
         <v>4485600</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4">
         <v>46150</v>
       </c>
-      <c r="C26" s="3">
+      <c r="D26" s="20">
         <v>38.1</v>
       </c>
-      <c r="D26" s="3">
+      <c r="E26" s="20">
         <v>38.35</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="20">
         <v>37.5</v>
       </c>
-      <c r="F26" s="6">
+      <c r="G26" s="21">
         <v>37.6</v>
       </c>
-      <c r="G26" s="21">
+      <c r="H26" s="19">
         <v>1959300</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4">
         <v>46153</v>
       </c>
-      <c r="C27" s="3">
+      <c r="D27" s="20">
         <v>38</v>
       </c>
-      <c r="D27" s="3">
+      <c r="E27" s="20">
         <v>38</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="20">
         <v>36.6</v>
       </c>
-      <c r="F27" s="6">
+      <c r="G27" s="21">
         <v>36.799999999999997</v>
       </c>
-      <c r="G27" s="21">
+      <c r="H27" s="19">
         <v>5094400</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4">
         <v>46154</v>
       </c>
-      <c r="C28" s="3">
+      <c r="D28" s="20">
         <v>37.200000000000003</v>
       </c>
-      <c r="D28" s="3">
+      <c r="E28" s="20">
         <v>37.9</v>
       </c>
-      <c r="E28" s="3">
+      <c r="F28" s="20">
         <v>37</v>
       </c>
-      <c r="F28" s="6">
+      <c r="G28" s="21">
         <v>37.799999999999997</v>
       </c>
-      <c r="G28" s="21">
+      <c r="H28" s="19">
         <v>1738800</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4">
         <v>46155</v>
       </c>
-      <c r="C29" s="3">
+      <c r="D29" s="20">
         <v>37.799999999999997</v>
       </c>
-      <c r="D29" s="3">
+      <c r="E29" s="20">
         <v>40.4</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="20">
         <v>37.5</v>
       </c>
-      <c r="F29" s="6">
+      <c r="G29" s="21">
         <v>40.35</v>
       </c>
-      <c r="G29" s="21">
+      <c r="H29" s="19">
         <v>10796000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4">
         <v>46156</v>
       </c>
-      <c r="C30" s="3">
+      <c r="D30" s="20">
         <v>40.5</v>
       </c>
-      <c r="D30" s="3">
+      <c r="E30" s="20">
         <v>41.75</v>
       </c>
-      <c r="E30" s="3">
+      <c r="F30" s="20">
         <v>39.75</v>
       </c>
-      <c r="F30" s="6">
+      <c r="G30" s="21">
         <v>39.85</v>
       </c>
-      <c r="G30" s="21">
+      <c r="H30" s="19">
         <v>5371100</v>
       </c>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4">
         <v>46157</v>
       </c>
-      <c r="C31" s="3">
+      <c r="D31" s="20">
         <v>39.4</v>
       </c>
-      <c r="D31" s="3">
+      <c r="E31" s="20">
         <v>42.35</v>
       </c>
-      <c r="E31" s="3">
+      <c r="F31" s="20">
         <v>39.4</v>
       </c>
-      <c r="F31" s="11">
+      <c r="G31" s="21">
         <v>42.2</v>
       </c>
-      <c r="G31" s="21">
+      <c r="H31" s="19">
         <v>9229000</v>
       </c>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="4">
         <v>46160</v>
       </c>
-      <c r="C32" s="3">
+      <c r="D32" s="20">
         <v>42.6</v>
       </c>
-      <c r="D32" s="3">
+      <c r="E32" s="20">
         <v>45.15</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="20">
         <v>42.5</v>
       </c>
-      <c r="F32" s="11">
+      <c r="G32" s="21">
         <v>45.15</v>
       </c>
-      <c r="G32" s="21">
+      <c r="H32" s="19">
         <v>11418400</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="4">
         <v>46161</v>
       </c>
-      <c r="C33" s="3">
+      <c r="D33" s="20">
         <v>46</v>
       </c>
-      <c r="D33" s="3">
+      <c r="E33" s="20">
         <v>47</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="20">
         <v>42</v>
       </c>
-      <c r="F33" s="11">
+      <c r="G33" s="21">
         <v>42</v>
       </c>
-      <c r="G33" s="21">
+      <c r="H33" s="19">
         <v>14765500</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="4">
         <v>46162</v>
       </c>
-      <c r="C34" s="3">
+      <c r="D34" s="20">
         <v>41.95</v>
       </c>
-      <c r="D34" s="3">
+      <c r="E34" s="20">
         <v>43.9</v>
       </c>
-      <c r="E34" s="3">
+      <c r="F34" s="20">
         <v>39.200000000000003</v>
       </c>
-      <c r="F34" s="11">
+      <c r="G34" s="21">
         <v>43.85</v>
       </c>
-      <c r="G34" s="21">
+      <c r="H34" s="19">
         <v>9839000</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="4">
         <v>46163</v>
       </c>
-      <c r="C35" s="3">
+      <c r="D35" s="20">
         <v>43.9</v>
       </c>
-      <c r="D35" s="3">
+      <c r="E35" s="20">
         <v>43.9</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="20">
         <v>42.25</v>
       </c>
-      <c r="F35" s="11">
+      <c r="G35" s="21">
         <v>42.95</v>
       </c>
-      <c r="G35" s="21">
+      <c r="H35" s="19">
         <v>3499000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="4">
         <v>46164</v>
       </c>
-      <c r="C36" s="3">
+      <c r="D36" s="20">
         <v>43.35</v>
       </c>
-      <c r="D36" s="3">
+      <c r="E36" s="20">
         <v>43.5</v>
       </c>
-      <c r="E36" s="3">
+      <c r="F36" s="20">
         <v>41.65</v>
       </c>
-      <c r="F36" s="11">
+      <c r="G36" s="21">
         <v>41.95</v>
       </c>
-      <c r="G36" s="21">
+      <c r="H36" s="19">
         <v>4139200</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="4">
         <v>46167</v>
       </c>
-      <c r="C37" s="3">
+      <c r="D37" s="20">
         <v>41</v>
       </c>
-      <c r="D37" s="3">
+      <c r="E37" s="20">
         <v>41.3</v>
       </c>
-      <c r="E37" s="3">
+      <c r="F37" s="20">
         <v>39.6</v>
       </c>
-      <c r="F37" s="11">
+      <c r="G37" s="21">
         <v>39.700000000000003</v>
       </c>
-      <c r="G37" s="21">
+      <c r="H37" s="19">
         <v>5757500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="4">
+        <v>46168</v>
+      </c>
+      <c r="D38" s="20">
+        <v>40.1</v>
+      </c>
+      <c r="E38" s="20">
+        <v>40.85</v>
+      </c>
+      <c r="F38" s="20">
+        <v>39.9</v>
+      </c>
+      <c r="G38" s="21">
+        <v>40</v>
+      </c>
+      <c r="H38" s="19">
+        <v>2009000</v>
       </c>
     </row>
   </sheetData>
@@ -1410,134 +1553,149 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="15"/>
-    <col min="3" max="3" width="15.5546875" style="15" customWidth="1"/>
-    <col min="4" max="4" width="47.5546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="15"/>
+    <col min="1" max="2" width="8.88671875" style="13"/>
+    <col min="3" max="3" width="15.5546875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="47.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="14"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="13">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="15">
+        <v>46157</v>
+      </c>
+      <c r="D2" s="16">
+        <f>AVERAGE('Lịch sử giá'!G2:G31)</f>
+        <v>39.326666666666668</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="14">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="15">
+        <v>46160</v>
+      </c>
+      <c r="D3" s="16">
+        <f>AVERAGE('Lịch sử giá'!G3:G32)</f>
+        <v>39.475000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="17">
-        <v>46157</v>
-      </c>
-      <c r="D2" s="18">
-        <f>AVERAGE('Lịch sử giá'!F2:F31)</f>
-        <v>39.326666666666668</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="16">
+      <c r="B4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="15">
+        <v>46161</v>
+      </c>
+      <c r="D4" s="16">
+        <f>AVERAGE('Lịch sử giá'!G4:G33)</f>
+        <v>39.528333333333336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="17">
-        <v>46160</v>
-      </c>
-      <c r="D3" s="18">
-        <f>AVERAGE('Lịch sử giá'!F3:F32)</f>
-        <v>39.475000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="16">
+      <c r="B5" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="15">
+        <v>46162</v>
+      </c>
+      <c r="D5" s="16">
+        <f>AVERAGE('Lịch sử giá'!G5:G34)</f>
+        <v>39.650000000000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="17">
-        <v>46161</v>
-      </c>
-      <c r="D4" s="18">
-        <f>AVERAGE('Lịch sử giá'!F4:F33)</f>
-        <v>39.528333333333336</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="16">
+      <c r="B6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="15">
+        <v>46163</v>
+      </c>
+      <c r="D6" s="16">
+        <f>AVERAGE('Lịch sử giá'!G6:G35)</f>
+        <v>39.785000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="14">
         <v>6</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="17">
-        <v>46162</v>
-      </c>
-      <c r="D5" s="18">
-        <f>AVERAGE('Lịch sử giá'!F5:F34)</f>
-        <v>39.650000000000006</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
+      <c r="B7" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="15">
+        <v>46164</v>
+      </c>
+      <c r="D7" s="16">
+        <f>AVERAGE('Lịch sử giá'!G7:G36)</f>
+        <v>39.896666666666675</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="17">
-        <v>46163</v>
-      </c>
-      <c r="D6" s="18">
-        <f>AVERAGE('Lịch sử giá'!F6:F35)</f>
-        <v>39.785000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="16">
+      <c r="B8" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="15">
+        <v>46167</v>
+      </c>
+      <c r="D8" s="16">
+        <f>AVERAGE('Lịch sử giá'!G8:G37)</f>
+        <v>39.870000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
         <v>8</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="17">
-        <v>46164</v>
-      </c>
-      <c r="D7" s="18">
-        <f>AVERAGE('Lịch sử giá'!F7:F36)</f>
-        <v>39.896666666666675</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="16">
-        <v>9</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="17">
-        <v>46167</v>
-      </c>
-      <c r="D8" s="18">
-        <f>AVERAGE('Lịch sử giá'!F8:F37)</f>
-        <v>39.870000000000005</v>
+      <c r="B9" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="15">
+        <v>46168</v>
+      </c>
+      <c r="D9" s="16">
+        <f>AVERAGE('Lịch sử giá'!G9:G38)</f>
+        <v>39.88666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F12BCEE9-4D5B-4AF4-8DC2-6F2AD0E03153}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E64A624-3212-4D8E-955C-FB2775F18AA0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,7 +69,7 @@
     <t>Giá đóng cửa</t>
   </si>
   <si>
-    <t>Khối lượng GD</t>
+    <t>KL</t>
   </si>
 </sst>
 </file>
@@ -195,10 +195,10 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E64A624-3212-4D8E-955C-FB2775F18AA0}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59525043-7089-4EBA-AC7C-E193BB084129}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -538,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1542,7 +1542,33 @@
         <v>40</v>
       </c>
       <c r="H38" s="19">
-        <v>2009000</v>
+        <v>2008600</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="4">
+        <v>46169</v>
+      </c>
+      <c r="D39" s="20">
+        <v>40.1</v>
+      </c>
+      <c r="E39" s="20">
+        <v>40.65</v>
+      </c>
+      <c r="F39" s="20">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="G39" s="21">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="H39" s="19">
+        <v>2735000</v>
       </c>
     </row>
   </sheetData>
@@ -1553,7 +1579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
@@ -1698,6 +1724,21 @@
         <v>39.88666666666667</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="15">
+        <v>46169</v>
+      </c>
+      <c r="D10" s="16">
+        <f>AVERAGE('Lịch sử giá'!G10:G39)</f>
+        <v>39.830000000000005</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59525043-7089-4EBA-AC7C-E193BB084129}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E226C2F-6992-43C2-B1DB-61B704DE898A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -538,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1568,7 +1568,33 @@
         <v>39.450000000000003</v>
       </c>
       <c r="H39" s="19">
-        <v>2735000</v>
+        <v>2735300</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="4">
+        <v>46170</v>
+      </c>
+      <c r="D40" s="20">
+        <v>39.35</v>
+      </c>
+      <c r="E40" s="20">
+        <v>40.5</v>
+      </c>
+      <c r="F40" s="20">
+        <v>38.85</v>
+      </c>
+      <c r="G40" s="21">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="H40" s="19">
+        <v>3792000</v>
       </c>
     </row>
   </sheetData>
@@ -1579,7 +1605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
@@ -1739,6 +1765,21 @@
         <v>39.830000000000005</v>
       </c>
     </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="15">
+        <v>46170</v>
+      </c>
+      <c r="D11" s="16">
+        <f>AVERAGE('Lịch sử giá'!G11:G40)</f>
+        <v>39.788333333333334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="268" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E226C2F-6992-43C2-B1DB-61B704DE898A}"/>
+  <xr:revisionPtr revIDLastSave="284" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58827894-1D05-498D-8F73-6BEAF6B7B74C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -538,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1594,7 +1594,33 @@
         <v>39.450000000000003</v>
       </c>
       <c r="H40" s="19">
-        <v>3792000</v>
+        <v>3792300</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="4">
+        <v>46171</v>
+      </c>
+      <c r="D41" s="21">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="E41" s="20">
+        <v>41.5</v>
+      </c>
+      <c r="F41" s="20">
+        <v>38.85</v>
+      </c>
+      <c r="G41" s="21">
+        <v>41</v>
+      </c>
+      <c r="H41" s="19">
+        <v>4645500</v>
       </c>
     </row>
   </sheetData>
@@ -1605,7 +1631,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
@@ -1780,6 +1806,21 @@
         <v>39.788333333333334</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="15">
+        <v>46171</v>
+      </c>
+      <c r="D12" s="16">
+        <f>AVERAGE('Lịch sử giá'!G12:G41)</f>
+        <v>39.816666666666677</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58827894-1D05-498D-8F73-6BEAF6B7B74C}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD35B872-A40D-4809-9894-B4E3BA0FCE44}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="12">
   <si>
     <t>Mã</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>KL</t>
+  </si>
+  <si>
+    <t>41.5</t>
   </si>
 </sst>
 </file>
@@ -538,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1623,6 +1626,32 @@
         <v>4645500</v>
       </c>
     </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="4">
+        <v>46174</v>
+      </c>
+      <c r="D42" s="21">
+        <v>41</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="20">
+        <v>39.75</v>
+      </c>
+      <c r="G42" s="21">
+        <v>39.75</v>
+      </c>
+      <c r="H42" s="19">
+        <v>2159000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1631,7 +1660,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
@@ -1821,6 +1850,21 @@
         <v>39.816666666666677</v>
       </c>
     </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="15">
+        <v>46174</v>
+      </c>
+      <c r="D13" s="16">
+        <f>AVERAGE('Lịch sử giá'!G13:G42)</f>
+        <v>39.815000000000012</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD35B872-A40D-4809-9894-B4E3BA0FCE44}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF528260-A546-4440-B24A-C17265A8CA1F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -71,15 +71,12 @@
   <si>
     <t>KL</t>
   </si>
-  <si>
-    <t>41.5</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -105,6 +102,10 @@
       <sz val="13"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -541,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1639,8 +1640,8 @@
       <c r="D42" s="21">
         <v>41</v>
       </c>
-      <c r="E42" s="20" t="s">
-        <v>11</v>
+      <c r="E42" s="20">
+        <v>41.5</v>
       </c>
       <c r="F42" s="20">
         <v>39.75</v>
@@ -1652,7 +1653,34 @@
         <v>2159000</v>
       </c>
     </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="4">
+        <v>46175</v>
+      </c>
+      <c r="D43" s="21">
+        <v>40.15</v>
+      </c>
+      <c r="E43" s="20">
+        <v>40.4</v>
+      </c>
+      <c r="F43" s="20">
+        <v>38.85</v>
+      </c>
+      <c r="G43" s="21">
+        <v>38.85</v>
+      </c>
+      <c r="H43" s="19">
+        <v>3073000</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1660,7 +1688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
@@ -1865,6 +1893,21 @@
         <v>39.815000000000012</v>
       </c>
     </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="11">
+        <v>13</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="15">
+        <v>46175</v>
+      </c>
+      <c r="D14" s="16">
+        <f>AVERAGE('Lịch sử giá'!G14:G43)</f>
+        <v>39.806666666666665</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF528260-A546-4440-B24A-C17265A8CA1F}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8033A80-014E-4DF4-BE49-86A3858F233E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -542,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1676,7 +1676,33 @@
         <v>38.85</v>
       </c>
       <c r="H43" s="19">
-        <v>3073000</v>
+        <v>3073400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="4">
+        <v>46176</v>
+      </c>
+      <c r="D44" s="21">
+        <v>38.85</v>
+      </c>
+      <c r="E44" s="20">
+        <v>39.85</v>
+      </c>
+      <c r="F44" s="20">
+        <v>38.85</v>
+      </c>
+      <c r="G44" s="21">
+        <v>39.15</v>
+      </c>
+      <c r="H44" s="19">
+        <v>1385000</v>
       </c>
     </row>
   </sheetData>
@@ -1688,7 +1714,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
@@ -1908,6 +1934,21 @@
         <v>39.806666666666665</v>
       </c>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="15">
+        <v>46176</v>
+      </c>
+      <c r="D15" s="16">
+        <f>AVERAGE('Lịch sử giá'!G15:G44)</f>
+        <v>39.780000000000008</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8033A80-014E-4DF4-BE49-86A3858F233E}"/>
+  <xr:revisionPtr revIDLastSave="329" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF0A0BD-A451-4E99-A2C5-4B5989D3F79F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -542,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1702,7 +1702,33 @@
         <v>39.15</v>
       </c>
       <c r="H44" s="19">
-        <v>1385000</v>
+        <v>1384800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="4">
+        <v>46177</v>
+      </c>
+      <c r="D45" s="21">
+        <v>40.450000000000003</v>
+      </c>
+      <c r="E45" s="20">
+        <v>41.85</v>
+      </c>
+      <c r="F45" s="20">
+        <v>40.35</v>
+      </c>
+      <c r="G45" s="21">
+        <v>41.85</v>
+      </c>
+      <c r="H45" s="19">
+        <v>6418000</v>
       </c>
     </row>
   </sheetData>
@@ -1714,7 +1740,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
@@ -1949,6 +1975,21 @@
         <v>39.780000000000008</v>
       </c>
     </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="11">
+        <v>15</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="15">
+        <v>46177</v>
+      </c>
+      <c r="D16" s="16">
+        <f>AVERAGE('Lịch sử giá'!G16:G45)</f>
+        <v>39.860000000000007</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="329" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF0A0BD-A451-4E99-A2C5-4B5989D3F79F}"/>
+  <xr:revisionPtr revIDLastSave="341" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{106CDA59-06DE-4D91-95DA-15D788F3A924}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lịch sử giá'!$D$1:$G$30</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1" iterateCount="1000" iterateDelta="0.01"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -106,6 +106,7 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -542,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1274,7 +1275,7 @@
       <c r="D28" s="20">
         <v>37.200000000000003</v>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="21">
         <v>37.9</v>
       </c>
       <c r="F28" s="20">
@@ -1300,7 +1301,7 @@
       <c r="D29" s="20">
         <v>37.799999999999997</v>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="21">
         <v>40.4</v>
       </c>
       <c r="F29" s="20">
@@ -1326,7 +1327,7 @@
       <c r="D30" s="20">
         <v>40.5</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="21">
         <v>41.75</v>
       </c>
       <c r="F30" s="20">
@@ -1353,7 +1354,7 @@
       <c r="D31" s="20">
         <v>39.4</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="21">
         <v>42.35</v>
       </c>
       <c r="F31" s="20">
@@ -1380,7 +1381,7 @@
       <c r="D32" s="20">
         <v>42.6</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="21">
         <v>45.15</v>
       </c>
       <c r="F32" s="20">
@@ -1406,7 +1407,7 @@
       <c r="D33" s="20">
         <v>46</v>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="21">
         <v>47</v>
       </c>
       <c r="F33" s="20">
@@ -1432,7 +1433,7 @@
       <c r="D34" s="20">
         <v>41.95</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="21">
         <v>43.9</v>
       </c>
       <c r="F34" s="20">
@@ -1458,7 +1459,7 @@
       <c r="D35" s="20">
         <v>43.9</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="21">
         <v>43.9</v>
       </c>
       <c r="F35" s="20">
@@ -1484,7 +1485,7 @@
       <c r="D36" s="20">
         <v>43.35</v>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="21">
         <v>43.5</v>
       </c>
       <c r="F36" s="20">
@@ -1510,7 +1511,7 @@
       <c r="D37" s="20">
         <v>41</v>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="21">
         <v>41.3</v>
       </c>
       <c r="F37" s="20">
@@ -1536,7 +1537,7 @@
       <c r="D38" s="20">
         <v>40.1</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="21">
         <v>40.85</v>
       </c>
       <c r="F38" s="20">
@@ -1562,7 +1563,7 @@
       <c r="D39" s="20">
         <v>40.1</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="21">
         <v>40.65</v>
       </c>
       <c r="F39" s="20">
@@ -1588,7 +1589,7 @@
       <c r="D40" s="20">
         <v>39.35</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="21">
         <v>40.5</v>
       </c>
       <c r="F40" s="20">
@@ -1614,7 +1615,7 @@
       <c r="D41" s="21">
         <v>39.450000000000003</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="21">
         <v>41.5</v>
       </c>
       <c r="F41" s="20">
@@ -1640,7 +1641,7 @@
       <c r="D42" s="21">
         <v>41</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="21">
         <v>41.5</v>
       </c>
       <c r="F42" s="20">
@@ -1666,7 +1667,7 @@
       <c r="D43" s="21">
         <v>40.15</v>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="21">
         <v>40.4</v>
       </c>
       <c r="F43" s="20">
@@ -1692,7 +1693,7 @@
       <c r="D44" s="21">
         <v>38.85</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="21">
         <v>39.85</v>
       </c>
       <c r="F44" s="20">
@@ -1718,7 +1719,7 @@
       <c r="D45" s="21">
         <v>40.450000000000003</v>
       </c>
-      <c r="E45" s="20">
+      <c r="E45" s="21">
         <v>41.85</v>
       </c>
       <c r="F45" s="20">
@@ -1729,6 +1730,32 @@
       </c>
       <c r="H45" s="19">
         <v>6418000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="4">
+        <v>46178</v>
+      </c>
+      <c r="D46" s="21">
+        <v>42.3</v>
+      </c>
+      <c r="E46" s="21">
+        <v>44</v>
+      </c>
+      <c r="F46" s="20">
+        <v>41.15</v>
+      </c>
+      <c r="G46" s="21">
+        <v>42</v>
+      </c>
+      <c r="H46" s="19">
+        <v>5041000</v>
       </c>
     </row>
   </sheetData>
@@ -1740,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
@@ -1990,6 +2017,21 @@
         <v>39.860000000000007</v>
       </c>
     </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="11">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="15">
+        <v>46178</v>
+      </c>
+      <c r="D17" s="16">
+        <f>AVERAGE('Lịch sử giá'!G17:G46)</f>
+        <v>39.948333333333345</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="341" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{106CDA59-06DE-4D91-95DA-15D788F3A924}"/>
+  <xr:revisionPtr revIDLastSave="357" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4C8153-9868-47E9-9D98-3D9A672EB72F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -220,10 +220,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -543,21 +539,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I46"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I47"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.86328125" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="9" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
@@ -583,7 +579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -599,7 +595,7 @@
       <c r="E2" s="20">
         <v>41.85</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>40.5</v>
       </c>
       <c r="G2" s="21">
@@ -610,7 +606,7 @@
       </c>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -626,7 +622,7 @@
       <c r="E3" s="20">
         <v>41.45</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="21">
         <v>40.049999999999997</v>
       </c>
       <c r="G3" s="21">
@@ -637,7 +633,7 @@
       </c>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -653,7 +649,7 @@
       <c r="E4" s="20">
         <v>41.35</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="21">
         <v>40.200000000000003</v>
       </c>
       <c r="G4" s="21">
@@ -664,7 +660,7 @@
       </c>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -680,7 +676,7 @@
       <c r="E5" s="20">
         <v>40.200000000000003</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="21">
         <v>38.9</v>
       </c>
       <c r="G5" s="21">
@@ -690,7 +686,7 @@
         <v>3124000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -706,7 +702,7 @@
       <c r="E6" s="20">
         <v>39.549999999999997</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>38.549999999999997</v>
       </c>
       <c r="G6" s="21">
@@ -716,7 +712,7 @@
         <v>1984000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -732,7 +728,7 @@
       <c r="E7" s="20">
         <v>40.75</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <v>38.950000000000003</v>
       </c>
       <c r="G7" s="21">
@@ -742,7 +738,7 @@
         <v>3490600</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -758,7 +754,7 @@
       <c r="E8" s="20">
         <v>40.5</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <v>39.5</v>
       </c>
       <c r="G8" s="21">
@@ -768,7 +764,7 @@
         <v>2983000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -784,7 +780,7 @@
       <c r="E9" s="20">
         <v>42</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <v>39.549999999999997</v>
       </c>
       <c r="G9" s="21">
@@ -794,7 +790,7 @@
         <v>5697200</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -810,7 +806,7 @@
       <c r="E10" s="20">
         <v>41.95</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <v>40.5</v>
       </c>
       <c r="G10" s="21">
@@ -820,7 +816,7 @@
         <v>3019000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -836,7 +832,7 @@
       <c r="E11" s="20">
         <v>41.2</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="21">
         <v>40.1</v>
       </c>
       <c r="G11" s="21">
@@ -846,7 +842,7 @@
         <v>2218200</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -862,7 +858,7 @@
       <c r="E12" s="20">
         <v>40.700000000000003</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <v>39.65</v>
       </c>
       <c r="G12" s="21">
@@ -872,7 +868,7 @@
         <v>2864800</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -888,7 +884,7 @@
       <c r="E13" s="20">
         <v>40.1</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <v>38.9</v>
       </c>
       <c r="G13" s="21">
@@ -898,7 +894,7 @@
         <v>3333400</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -914,7 +910,7 @@
       <c r="E14" s="20">
         <v>40.450000000000003</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <v>38.950000000000003</v>
       </c>
       <c r="G14" s="21">
@@ -924,7 +920,7 @@
         <v>2901300</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -940,7 +936,7 @@
       <c r="E15" s="20">
         <v>40.299999999999997</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="21">
         <v>39.299999999999997</v>
       </c>
       <c r="G15" s="21">
@@ -950,7 +946,7 @@
         <v>1765400</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -966,7 +962,7 @@
       <c r="E16" s="20">
         <v>40</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <v>39.299999999999997</v>
       </c>
       <c r="G16" s="21">
@@ -976,7 +972,7 @@
         <v>1986400</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -992,7 +988,7 @@
       <c r="E17" s="20">
         <v>39.6</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <v>39</v>
       </c>
       <c r="G17" s="21">
@@ -1002,7 +998,7 @@
         <v>1910900</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1018,7 +1014,7 @@
       <c r="E18" s="20">
         <v>39.700000000000003</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="21">
         <v>38</v>
       </c>
       <c r="G18" s="21">
@@ -1028,7 +1024,7 @@
         <v>3786500</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1044,7 +1040,7 @@
       <c r="E19" s="20">
         <v>41.35</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="21">
         <v>39.549999999999997</v>
       </c>
       <c r="G19" s="21">
@@ -1054,7 +1050,7 @@
         <v>6401800</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1070,7 +1066,7 @@
       <c r="E20" s="20">
         <v>39.200000000000003</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="21">
         <v>36.950000000000003</v>
       </c>
       <c r="G20" s="21">
@@ -1080,7 +1076,7 @@
         <v>6503400</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1096,7 +1092,7 @@
       <c r="E21" s="20">
         <v>37.450000000000003</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="21">
         <v>36.25</v>
       </c>
       <c r="G21" s="21">
@@ -1106,7 +1102,7 @@
         <v>3564100</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1122,7 +1118,7 @@
       <c r="E22" s="20">
         <v>39.75</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="21">
         <v>38.1</v>
       </c>
       <c r="G22" s="21">
@@ -1132,7 +1128,7 @@
         <v>4403600</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1148,7 +1144,7 @@
       <c r="E23" s="20">
         <v>39.700000000000003</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="21">
         <v>37.799999999999997</v>
       </c>
       <c r="G23" s="21">
@@ -1158,7 +1154,7 @@
         <v>3878000</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1174,7 +1170,7 @@
       <c r="E24" s="20">
         <v>39.6</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="21">
         <v>38.65</v>
       </c>
       <c r="G24" s="21">
@@ -1184,7 +1180,7 @@
         <v>3098200</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1200,7 +1196,7 @@
       <c r="E25" s="20">
         <v>38.9</v>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="21">
         <v>37.700000000000003</v>
       </c>
       <c r="G25" s="21">
@@ -1210,7 +1206,7 @@
         <v>4485600</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1226,7 +1222,7 @@
       <c r="E26" s="20">
         <v>38.35</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="21">
         <v>37.5</v>
       </c>
       <c r="G26" s="21">
@@ -1236,7 +1232,7 @@
         <v>1959300</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1252,7 +1248,7 @@
       <c r="E27" s="20">
         <v>38</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="21">
         <v>36.6</v>
       </c>
       <c r="G27" s="21">
@@ -1262,7 +1258,7 @@
         <v>5094400</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1278,7 +1274,7 @@
       <c r="E28" s="21">
         <v>37.9</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="21">
         <v>37</v>
       </c>
       <c r="G28" s="21">
@@ -1288,7 +1284,7 @@
         <v>1738800</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1304,7 +1300,7 @@
       <c r="E29" s="21">
         <v>40.4</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29" s="21">
         <v>37.5</v>
       </c>
       <c r="G29" s="21">
@@ -1314,7 +1310,7 @@
         <v>10796000</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1330,7 +1326,7 @@
       <c r="E30" s="21">
         <v>41.75</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="21">
         <v>39.75</v>
       </c>
       <c r="G30" s="21">
@@ -1341,7 +1337,7 @@
       </c>
       <c r="I30" s="5"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -1357,7 +1353,7 @@
       <c r="E31" s="21">
         <v>42.35</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="21">
         <v>39.4</v>
       </c>
       <c r="G31" s="21">
@@ -1368,7 +1364,7 @@
       </c>
       <c r="I31" s="5"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -1384,7 +1380,7 @@
       <c r="E32" s="21">
         <v>45.15</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="21">
         <v>42.5</v>
       </c>
       <c r="G32" s="21">
@@ -1394,7 +1390,7 @@
         <v>11418400</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -1410,7 +1406,7 @@
       <c r="E33" s="21">
         <v>47</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="21">
         <v>42</v>
       </c>
       <c r="G33" s="21">
@@ -1420,7 +1416,7 @@
         <v>14765500</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1436,7 +1432,7 @@
       <c r="E34" s="21">
         <v>43.9</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="21">
         <v>39.200000000000003</v>
       </c>
       <c r="G34" s="21">
@@ -1446,7 +1442,7 @@
         <v>9839000</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1462,7 +1458,7 @@
       <c r="E35" s="21">
         <v>43.9</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="21">
         <v>42.25</v>
       </c>
       <c r="G35" s="21">
@@ -1472,7 +1468,7 @@
         <v>3499000</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1488,7 +1484,7 @@
       <c r="E36" s="21">
         <v>43.5</v>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="21">
         <v>41.65</v>
       </c>
       <c r="G36" s="21">
@@ -1498,7 +1494,7 @@
         <v>4139200</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -1514,7 +1510,7 @@
       <c r="E37" s="21">
         <v>41.3</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="21">
         <v>39.6</v>
       </c>
       <c r="G37" s="21">
@@ -1524,7 +1520,7 @@
         <v>5757500</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1540,7 +1536,7 @@
       <c r="E38" s="21">
         <v>40.85</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="21">
         <v>39.9</v>
       </c>
       <c r="G38" s="21">
@@ -1550,7 +1546,7 @@
         <v>2008600</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -1566,7 +1562,7 @@
       <c r="E39" s="21">
         <v>40.65</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="21">
         <v>39.450000000000003</v>
       </c>
       <c r="G39" s="21">
@@ -1576,7 +1572,7 @@
         <v>2735300</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -1592,7 +1588,7 @@
       <c r="E40" s="21">
         <v>40.5</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="21">
         <v>38.85</v>
       </c>
       <c r="G40" s="21">
@@ -1602,7 +1598,7 @@
         <v>3792300</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -1618,7 +1614,7 @@
       <c r="E41" s="21">
         <v>41.5</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="21">
         <v>38.85</v>
       </c>
       <c r="G41" s="21">
@@ -1628,7 +1624,7 @@
         <v>4645500</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -1644,7 +1640,7 @@
       <c r="E42" s="21">
         <v>41.5</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="21">
         <v>39.75</v>
       </c>
       <c r="G42" s="21">
@@ -1654,7 +1650,7 @@
         <v>2159000</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -1670,7 +1666,7 @@
       <c r="E43" s="21">
         <v>40.4</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="21">
         <v>38.85</v>
       </c>
       <c r="G43" s="21">
@@ -1680,7 +1676,7 @@
         <v>3073400</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -1696,7 +1692,7 @@
       <c r="E44" s="21">
         <v>39.85</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="21">
         <v>38.85</v>
       </c>
       <c r="G44" s="21">
@@ -1706,7 +1702,7 @@
         <v>1384800</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -1722,7 +1718,7 @@
       <c r="E45" s="21">
         <v>41.85</v>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="21">
         <v>40.35</v>
       </c>
       <c r="G45" s="21">
@@ -1732,7 +1728,7 @@
         <v>6418000</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -1748,7 +1744,7 @@
       <c r="E46" s="21">
         <v>44</v>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="21">
         <v>41.15</v>
       </c>
       <c r="G46" s="21">
@@ -1756,6 +1752,32 @@
       </c>
       <c r="H46" s="19">
         <v>5041000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="4">
+        <v>46181</v>
+      </c>
+      <c r="D47" s="21">
+        <v>41.6</v>
+      </c>
+      <c r="E47" s="21">
+        <v>42.8</v>
+      </c>
+      <c r="F47" s="21">
+        <v>41.5</v>
+      </c>
+      <c r="G47" s="21">
+        <v>41.7</v>
+      </c>
+      <c r="H47" s="19">
+        <v>3844100</v>
       </c>
     </row>
   </sheetData>
@@ -1767,17 +1789,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="13"/>
-    <col min="3" max="3" width="15.5546875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="47.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="13"/>
+    <col min="1" max="2" width="8.86328125" style="13"/>
+    <col min="3" max="3" width="15.53125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="47.53125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.86328125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
@@ -1792,7 +1814,7 @@
       </c>
       <c r="E1" s="12"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -1807,7 +1829,7 @@
         <v>39.326666666666668</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -1822,7 +1844,7 @@
         <v>39.475000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="11">
         <v>3</v>
       </c>
@@ -1837,7 +1859,7 @@
         <v>39.528333333333336</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -1852,7 +1874,7 @@
         <v>39.650000000000006</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="11">
         <v>5</v>
       </c>
@@ -1867,7 +1889,7 @@
         <v>39.785000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="14">
         <v>6</v>
       </c>
@@ -1882,7 +1904,7 @@
         <v>39.896666666666675</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="11">
         <v>7</v>
       </c>
@@ -1897,7 +1919,7 @@
         <v>39.870000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -1912,7 +1934,7 @@
         <v>39.88666666666667</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="11">
         <v>9</v>
       </c>
@@ -1927,7 +1949,7 @@
         <v>39.830000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="11">
         <v>10</v>
       </c>
@@ -1942,7 +1964,7 @@
         <v>39.788333333333334</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="11">
         <v>11</v>
       </c>
@@ -1957,7 +1979,7 @@
         <v>39.816666666666677</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -1972,7 +1994,7 @@
         <v>39.815000000000012</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="11">
         <v>13</v>
       </c>
@@ -1987,7 +2009,7 @@
         <v>39.806666666666665</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="11">
         <v>14</v>
       </c>
@@ -2002,7 +2024,7 @@
         <v>39.780000000000008</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="11">
         <v>15</v>
       </c>
@@ -2017,7 +2039,7 @@
         <v>39.860000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="11">
         <v>16</v>
       </c>
@@ -2030,6 +2052,21 @@
       <c r="D17" s="16">
         <f>AVERAGE('Lịch sử giá'!G17:G46)</f>
         <v>39.948333333333345</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" s="11">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="15">
+        <v>46181</v>
+      </c>
+      <c r="D18" s="16">
+        <f>AVERAGE('Lịch sử giá'!G18:G47)</f>
+        <v>40.038333333333341</v>
       </c>
     </row>
   </sheetData>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="357" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4C8153-9868-47E9-9D98-3D9A672EB72F}"/>
+  <xr:revisionPtr revIDLastSave="366" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67C0CB25-151E-4932-BC74-82404E11E3AA}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -1780,6 +1780,32 @@
         <v>3844100</v>
       </c>
     </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="4">
+        <v>46182</v>
+      </c>
+      <c r="D48" s="21">
+        <v>41.8</v>
+      </c>
+      <c r="E48" s="21">
+        <v>41.8</v>
+      </c>
+      <c r="F48" s="21">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="G48" s="21">
+        <v>40.5</v>
+      </c>
+      <c r="H48" s="19">
+        <v>2504400</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1789,7 +1815,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2069,6 +2095,21 @@
         <v>40.038333333333341</v>
       </c>
     </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="11">
+        <v>18</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="15">
+        <v>46182</v>
+      </c>
+      <c r="D19" s="16">
+        <f>AVERAGE('Lịch sử giá'!G19:G48)</f>
+        <v>40.078333333333347</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="366" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67C0CB25-151E-4932-BC74-82404E11E3AA}"/>
+  <xr:revisionPtr revIDLastSave="374" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D44606D-32AD-474F-8BB7-37EA09DB108B}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -1806,6 +1806,32 @@
         <v>2504400</v>
       </c>
     </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="4">
+        <v>46183</v>
+      </c>
+      <c r="D49" s="21">
+        <v>40.9</v>
+      </c>
+      <c r="E49" s="21">
+        <v>40.950000000000003</v>
+      </c>
+      <c r="F49" s="21">
+        <v>39.85</v>
+      </c>
+      <c r="G49" s="21">
+        <v>40.049999999999997</v>
+      </c>
+      <c r="H49" s="19">
+        <v>2594400</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1815,7 +1841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2110,6 +2136,21 @@
         <v>40.078333333333347</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" s="11">
+        <v>19</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="15">
+        <v>46183</v>
+      </c>
+      <c r="D20" s="16">
+        <f>AVERAGE('Lịch sử giá'!G20:G49)</f>
+        <v>40.090000000000011</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="374" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D44606D-32AD-474F-8BB7-37EA09DB108B}"/>
+  <xr:revisionPtr revIDLastSave="382" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC4DEB34-CDD9-4B2C-B28A-359024E70E9B}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -1832,6 +1832,32 @@
         <v>2594400</v>
       </c>
     </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="4">
+        <v>46184</v>
+      </c>
+      <c r="D50" s="21">
+        <v>40.6</v>
+      </c>
+      <c r="E50" s="21">
+        <v>40.950000000000003</v>
+      </c>
+      <c r="F50" s="21">
+        <v>39.85</v>
+      </c>
+      <c r="G50" s="21">
+        <v>39.85</v>
+      </c>
+      <c r="H50" s="19">
+        <v>1687000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1841,7 +1867,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2151,6 +2177,21 @@
         <v>40.090000000000011</v>
       </c>
     </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" s="11">
+        <v>20</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="15">
+        <v>46184</v>
+      </c>
+      <c r="D21" s="16">
+        <f>AVERAGE('Lịch sử giá'!G21:G50)</f>
+        <v>40.186666666666675</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="382" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC4DEB34-CDD9-4B2C-B28A-359024E70E9B}"/>
+  <xr:revisionPtr revIDLastSave="390" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{373CC146-57D4-45A9-860F-8A5CA360C01A}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -1858,6 +1858,32 @@
         <v>1687000</v>
       </c>
     </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="4">
+        <v>46185</v>
+      </c>
+      <c r="D51" s="21">
+        <v>39.85</v>
+      </c>
+      <c r="E51" s="21">
+        <v>41</v>
+      </c>
+      <c r="F51" s="21">
+        <v>39.65</v>
+      </c>
+      <c r="G51" s="21">
+        <v>40.049999999999997</v>
+      </c>
+      <c r="H51" s="19">
+        <v>2261400</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1867,7 +1893,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2192,6 +2218,21 @@
         <v>40.186666666666675</v>
       </c>
     </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" s="11">
+        <v>21</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="15">
+        <v>46185</v>
+      </c>
+      <c r="D22" s="16">
+        <f>AVERAGE('Lịch sử giá'!G22:G51)</f>
+        <v>40.283333333333331</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{373CC146-57D4-45A9-860F-8A5CA360C01A}"/>
+  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD1010C2-1A6A-43E1-AE72-13D9A2C267F0}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -1884,6 +1884,32 @@
         <v>2261400</v>
       </c>
     </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="4">
+        <v>46188</v>
+      </c>
+      <c r="D52" s="21">
+        <v>39.4</v>
+      </c>
+      <c r="E52" s="21">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="F52" s="21">
+        <v>38.4</v>
+      </c>
+      <c r="G52" s="21">
+        <v>38.5</v>
+      </c>
+      <c r="H52" s="19">
+        <v>4536400</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1893,7 +1919,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2233,6 +2259,21 @@
         <v>40.283333333333331</v>
       </c>
     </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" s="11">
+        <v>22</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="15">
+        <v>46188</v>
+      </c>
+      <c r="D23" s="16">
+        <f>AVERAGE('Lịch sử giá'!G23:G52)</f>
+        <v>40.276666666666671</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD1010C2-1A6A-43E1-AE72-13D9A2C267F0}"/>
+  <xr:revisionPtr revIDLastSave="415" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{141FE5F0-D8E9-4CDB-8B4D-EADB65E899E6}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -1127,6 +1127,7 @@
       <c r="H22" s="19">
         <v>4403600</v>
       </c>
+      <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
@@ -1153,6 +1154,7 @@
       <c r="H23" s="19">
         <v>3878000</v>
       </c>
+      <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
@@ -1908,6 +1910,32 @@
       </c>
       <c r="H52" s="19">
         <v>4536400</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="4">
+        <v>46189</v>
+      </c>
+      <c r="D53" s="21">
+        <v>38.75</v>
+      </c>
+      <c r="E53" s="21">
+        <v>39</v>
+      </c>
+      <c r="F53" s="21">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="G53" s="21">
+        <v>38.6</v>
+      </c>
+      <c r="H53" s="19">
+        <v>1880400</v>
       </c>
     </row>
   </sheetData>
@@ -1919,7 +1947,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2274,6 +2302,21 @@
         <v>40.276666666666671</v>
       </c>
     </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" s="11">
+        <v>23</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="15">
+        <v>46189</v>
+      </c>
+      <c r="D24" s="16">
+        <f>AVERAGE('Lịch sử giá'!G24:G53)</f>
+        <v>40.255000000000003</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="415" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{141FE5F0-D8E9-4CDB-8B4D-EADB65E899E6}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BB7EB5F-3906-403D-AFD4-FC60EDEBEAE1}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -1938,6 +1938,32 @@
         <v>1880400</v>
       </c>
     </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="4">
+        <v>46190</v>
+      </c>
+      <c r="D54" s="21">
+        <v>38.6</v>
+      </c>
+      <c r="E54" s="21">
+        <v>39.4</v>
+      </c>
+      <c r="F54" s="21">
+        <v>38.25</v>
+      </c>
+      <c r="G54" s="21">
+        <v>38.65</v>
+      </c>
+      <c r="H54" s="19">
+        <v>1724200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1947,7 +1973,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2317,6 +2343,21 @@
         <v>40.255000000000003</v>
       </c>
     </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" s="11">
+        <v>24</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="15">
+        <v>46190</v>
+      </c>
+      <c r="D25" s="16">
+        <f>AVERAGE('Lịch sử giá'!G25:G54)</f>
+        <v>40.243333333333332</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="423" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BB7EB5F-3906-403D-AFD4-FC60EDEBEAE1}"/>
+  <xr:revisionPtr revIDLastSave="431" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9715F97B-219D-4C5B-85DE-BCB1CB2B02B5}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -1964,6 +1964,32 @@
         <v>1724200</v>
       </c>
     </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="4">
+        <v>46191</v>
+      </c>
+      <c r="D55" s="21">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="E55" s="21">
+        <v>39.25</v>
+      </c>
+      <c r="F55" s="21">
+        <v>38.6</v>
+      </c>
+      <c r="G55" s="21">
+        <v>39</v>
+      </c>
+      <c r="H55" s="19">
+        <v>1549000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1973,7 +1999,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2358,6 +2384,21 @@
         <v>40.243333333333332</v>
       </c>
     </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" s="11">
+        <v>25</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="15">
+        <v>46191</v>
+      </c>
+      <c r="D26" s="16">
+        <f>AVERAGE('Lịch sử giá'!G26:G55)</f>
+        <v>40.286666666666669</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="431" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9715F97B-219D-4C5B-85DE-BCB1CB2B02B5}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61D455DA-DAD8-4549-80FC-4AA4487B60AB}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -220,6 +220,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -539,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -1990,6 +1994,32 @@
         <v>1549000</v>
       </c>
     </row>
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="4">
+        <v>46192</v>
+      </c>
+      <c r="D56" s="21">
+        <v>39.1</v>
+      </c>
+      <c r="E56" s="21">
+        <v>39.15</v>
+      </c>
+      <c r="F56" s="21">
+        <v>38.6</v>
+      </c>
+      <c r="G56" s="21">
+        <v>38.65</v>
+      </c>
+      <c r="H56" s="19">
+        <v>1532600</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1999,7 +2029,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2399,6 +2429,21 @@
         <v>40.286666666666669</v>
       </c>
     </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" s="11">
+        <v>26</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="15">
+        <v>46192</v>
+      </c>
+      <c r="D27" s="16">
+        <f>AVERAGE('Lịch sử giá'!G27:G56)</f>
+        <v>40.321666666666673</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61D455DA-DAD8-4549-80FC-4AA4487B60AB}"/>
+  <xr:revisionPtr revIDLastSave="450" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0CBA8F0-72A8-4BD1-9FD5-87E27847231D}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -543,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2020,6 +2020,32 @@
         <v>1532600</v>
       </c>
     </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="4">
+        <v>46195</v>
+      </c>
+      <c r="D57" s="21">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E57" s="21">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="F57" s="21">
+        <v>38.65</v>
+      </c>
+      <c r="G57" s="21">
+        <v>38.65</v>
+      </c>
+      <c r="H57" s="19">
+        <v>1872100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2029,7 +2055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2444,6 +2470,21 @@
         <v>40.321666666666673</v>
       </c>
     </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" s="11">
+        <v>27</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="15">
+        <v>46195</v>
+      </c>
+      <c r="D28" s="16">
+        <f>AVERAGE('Lịch sử giá'!G28:G57)</f>
+        <v>40.38333333333334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="450" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0CBA8F0-72A8-4BD1-9FD5-87E27847231D}"/>
+  <xr:revisionPtr revIDLastSave="477" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{110108D8-D016-4D11-A389-AFE06B8F750B}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -220,10 +220,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -543,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -557,7 +553,7 @@
     <col min="9" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
@@ -583,7 +579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -608,9 +604,8 @@
       <c r="H2" s="19">
         <v>4263100</v>
       </c>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -635,9 +630,8 @@
       <c r="H3" s="19">
         <v>2560600</v>
       </c>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -662,9 +656,8 @@
       <c r="H4" s="19">
         <v>2933800</v>
       </c>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -690,7 +683,7 @@
         <v>3124000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -716,7 +709,7 @@
         <v>1984000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -742,7 +735,7 @@
         <v>3490600</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -768,7 +761,7 @@
         <v>2983000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -794,7 +787,7 @@
         <v>5697200</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -820,7 +813,7 @@
         <v>3019000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -846,7 +839,7 @@
         <v>2218200</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -872,7 +865,7 @@
         <v>2864800</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -898,7 +891,7 @@
         <v>3333400</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -924,7 +917,7 @@
         <v>2901300</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -950,7 +943,7 @@
         <v>1765400</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -976,7 +969,7 @@
         <v>1986400</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1002,7 +995,7 @@
         <v>1910900</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1028,7 +1021,7 @@
         <v>3786500</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1054,7 +1047,7 @@
         <v>6401800</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1080,7 +1073,7 @@
         <v>6503400</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1106,7 +1099,7 @@
         <v>3564100</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1131,9 +1124,8 @@
       <c r="H22" s="19">
         <v>4403600</v>
       </c>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1158,9 +1150,8 @@
       <c r="H23" s="19">
         <v>3878000</v>
       </c>
-      <c r="I23" s="5"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1186,7 +1177,7 @@
         <v>3098200</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1212,7 +1203,7 @@
         <v>4485600</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1238,7 +1229,7 @@
         <v>1959300</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1264,7 +1255,7 @@
         <v>5094400</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1290,7 +1281,7 @@
         <v>1738800</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1316,7 +1307,7 @@
         <v>10796000</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1341,9 +1332,8 @@
       <c r="H30" s="19">
         <v>5371100</v>
       </c>
-      <c r="I30" s="5"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -1368,9 +1358,8 @@
       <c r="H31" s="19">
         <v>9229000</v>
       </c>
-      <c r="I31" s="5"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -1812,7 +1801,7 @@
         <v>2504400</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -1838,7 +1827,7 @@
         <v>2594400</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -1864,7 +1853,7 @@
         <v>1687000</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -1890,7 +1879,7 @@
         <v>2261400</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -1916,7 +1905,7 @@
         <v>4536400</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -1942,7 +1931,7 @@
         <v>1880400</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -1968,7 +1957,7 @@
         <v>1724200</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -1994,7 +1983,7 @@
         <v>1549000</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -2020,7 +2009,7 @@
         <v>1532600</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -2045,6 +2034,33 @@
       <c r="H57" s="19">
         <v>1872100</v>
       </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="4">
+        <v>46196</v>
+      </c>
+      <c r="D58" s="21">
+        <v>38.9</v>
+      </c>
+      <c r="E58" s="21">
+        <v>38.9</v>
+      </c>
+      <c r="F58" s="21">
+        <v>37.450000000000003</v>
+      </c>
+      <c r="G58" s="21">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="H58" s="19">
+        <v>4318200</v>
+      </c>
+      <c r="K58" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2055,7 +2071,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2485,6 +2501,21 @@
         <v>40.38333333333334</v>
       </c>
     </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" s="11">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="15">
+        <v>46196</v>
+      </c>
+      <c r="D29" s="16">
+        <f>AVERAGE('Lịch sử giá'!G29:G58)</f>
+        <v>40.38000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="477" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{110108D8-D016-4D11-A389-AFE06B8F750B}"/>
+  <xr:revisionPtr revIDLastSave="485" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84269E4B-7F5D-481B-8C5A-FDA855A2C725}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2062,6 +2062,32 @@
       </c>
       <c r="K58" s="5"/>
     </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="4">
+        <v>46197</v>
+      </c>
+      <c r="D59" s="21">
+        <v>37.75</v>
+      </c>
+      <c r="E59" s="21">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="F59" s="21">
+        <v>36.85</v>
+      </c>
+      <c r="G59" s="21">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="H59" s="19">
+        <v>1914700</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2071,7 +2097,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2516,6 +2542,21 @@
         <v>40.38000000000001</v>
       </c>
     </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" s="11">
+        <v>29</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="15">
+        <v>46197</v>
+      </c>
+      <c r="D30" s="16">
+        <f>AVERAGE('Lịch sử giá'!G30:G59)</f>
+        <v>40.295000000000002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="485" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84269E4B-7F5D-481B-8C5A-FDA855A2C725}"/>
+  <xr:revisionPtr revIDLastSave="495" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D6E93BD-EB68-4565-9BF2-8D444C8E8214}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2088,6 +2088,32 @@
         <v>1914700</v>
       </c>
     </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="4">
+        <v>46198</v>
+      </c>
+      <c r="D60" s="21">
+        <v>37.75</v>
+      </c>
+      <c r="E60" s="21">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="F60" s="21">
+        <v>37</v>
+      </c>
+      <c r="G60" s="21">
+        <v>37.25</v>
+      </c>
+      <c r="H60" s="19">
+        <v>907100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2097,7 +2123,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2557,6 +2583,21 @@
         <v>40.295000000000002</v>
       </c>
     </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" s="11">
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="15">
+        <v>46198</v>
+      </c>
+      <c r="D31" s="16">
+        <f>AVERAGE('Lịch sử giá'!G31:G60)</f>
+        <v>40.208333333333336</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="495" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D6E93BD-EB68-4565-9BF2-8D444C8E8214}"/>
+  <xr:revisionPtr revIDLastSave="507" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F053EED2-AFD8-49BB-A1CC-B30168219E71}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -220,6 +220,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -539,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2114,6 +2118,32 @@
         <v>907100</v>
       </c>
     </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A61" s="3">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="4">
+        <v>46199</v>
+      </c>
+      <c r="D61" s="21">
+        <v>37.4</v>
+      </c>
+      <c r="E61" s="21">
+        <v>37.549999999999997</v>
+      </c>
+      <c r="F61" s="21">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="G61" s="21">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="H61" s="19">
+        <v>1716200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2123,7 +2153,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2598,6 +2628,21 @@
         <v>40.208333333333336</v>
       </c>
     </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="11">
+        <v>31</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="15">
+        <v>46199</v>
+      </c>
+      <c r="D32" s="16">
+        <f>AVERAGE('Lịch sử giá'!G32:G61)</f>
+        <v>40.028333333333329</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="507" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F053EED2-AFD8-49BB-A1CC-B30168219E71}"/>
+  <xr:revisionPtr revIDLastSave="517" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D795DEE3-F9A5-4C06-B53C-4D7BC92FE139}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -220,10 +220,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -543,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2144,6 +2140,32 @@
         <v>1716200</v>
       </c>
     </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="4">
+        <v>46202</v>
+      </c>
+      <c r="D62" s="21">
+        <v>36.9</v>
+      </c>
+      <c r="E62" s="21">
+        <v>37.75</v>
+      </c>
+      <c r="F62" s="21">
+        <v>36.85</v>
+      </c>
+      <c r="G62" s="21">
+        <v>37.25</v>
+      </c>
+      <c r="H62" s="19">
+        <v>1256200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2153,7 +2175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2643,6 +2665,21 @@
         <v>40.028333333333329</v>
       </c>
     </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" s="11">
+        <v>32</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="15">
+        <v>46202</v>
+      </c>
+      <c r="D33" s="16">
+        <f>AVERAGE('Lịch sử giá'!G33:G62)</f>
+        <v>39.764999999999993</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="517" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D795DEE3-F9A5-4C06-B53C-4D7BC92FE139}"/>
+  <xr:revisionPtr revIDLastSave="542" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD155D26-9DA1-474D-BA6C-0219F2044AD8}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2165,6 +2165,33 @@
       <c r="H62" s="19">
         <v>1256200</v>
       </c>
+      <c r="I62" s="5"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A63" s="3">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="4">
+        <v>46203</v>
+      </c>
+      <c r="D63" s="21">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="E63" s="21">
+        <v>37.6</v>
+      </c>
+      <c r="F63" s="21">
+        <v>36.9</v>
+      </c>
+      <c r="G63" s="21">
+        <v>36.950000000000003</v>
+      </c>
+      <c r="H63" s="19">
+        <v>1153800</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2175,7 +2202,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2680,6 +2707,21 @@
         <v>39.764999999999993</v>
       </c>
     </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" s="11">
+        <v>33</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="15">
+        <v>46203</v>
+      </c>
+      <c r="D34" s="16">
+        <f>AVERAGE('Lịch sử giá'!G34:G63)</f>
+        <v>39.596666666666671</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="542" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD155D26-9DA1-474D-BA6C-0219F2044AD8}"/>
+  <xr:revisionPtr revIDLastSave="552" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF2D2D5D-E2FD-47D9-92C6-B464B22299AF}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2193,6 +2193,32 @@
         <v>1153800</v>
       </c>
     </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="4">
+        <v>46204</v>
+      </c>
+      <c r="D64" s="21">
+        <v>36.950000000000003</v>
+      </c>
+      <c r="E64" s="21">
+        <v>38.5</v>
+      </c>
+      <c r="F64" s="21">
+        <v>36.950000000000003</v>
+      </c>
+      <c r="G64" s="21">
+        <v>37.450000000000003</v>
+      </c>
+      <c r="H64" s="19">
+        <v>1561500</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2202,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2722,6 +2748,21 @@
         <v>39.596666666666671</v>
       </c>
     </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" s="11">
+        <v>34</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="15">
+        <v>46204</v>
+      </c>
+      <c r="D35" s="16">
+        <f>AVERAGE('Lịch sử giá'!G35:G64)</f>
+        <v>39.383333333333333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="552" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF2D2D5D-E2FD-47D9-92C6-B464B22299AF}"/>
+  <xr:revisionPtr revIDLastSave="560" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB218B7C-10D8-47D7-9540-6AC6EC31835F}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2219,6 +2219,32 @@
         <v>1561500</v>
       </c>
     </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A65" s="3">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="4">
+        <v>46205</v>
+      </c>
+      <c r="D65" s="21">
+        <v>37.450000000000003</v>
+      </c>
+      <c r="E65" s="21">
+        <v>37.450000000000003</v>
+      </c>
+      <c r="F65" s="21">
+        <v>37.1</v>
+      </c>
+      <c r="G65" s="21">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="H65" s="19">
+        <v>803400</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2228,7 +2254,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2763,6 +2789,21 @@
         <v>39.383333333333333</v>
       </c>
     </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" s="11">
+        <v>35</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="15">
+        <v>46205</v>
+      </c>
+      <c r="D36" s="16">
+        <f>AVERAGE('Lịch sử giá'!G36:G65)</f>
+        <v>39.19166666666667</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="560" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB218B7C-10D8-47D7-9540-6AC6EC31835F}"/>
+  <xr:revisionPtr revIDLastSave="570" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11EBE9B2-AC74-4A7F-BD20-6D2118FB1007}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2245,6 +2245,32 @@
         <v>803400</v>
       </c>
     </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A66" s="3">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" s="4">
+        <v>46206</v>
+      </c>
+      <c r="D66" s="21">
+        <v>37.450000000000003</v>
+      </c>
+      <c r="E66" s="21">
+        <v>37.450000000000003</v>
+      </c>
+      <c r="F66" s="21">
+        <v>36.549999999999997</v>
+      </c>
+      <c r="G66" s="21">
+        <v>36.549999999999997</v>
+      </c>
+      <c r="H66" s="19">
+        <v>2066900</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2254,7 +2280,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2804,6 +2830,21 @@
         <v>39.19166666666667</v>
       </c>
     </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" s="11">
+        <v>36</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="15">
+        <v>46206</v>
+      </c>
+      <c r="D37" s="16">
+        <f>AVERAGE('Lịch sử giá'!G37:G66)</f>
+        <v>39.011666666666663</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="570" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11EBE9B2-AC74-4A7F-BD20-6D2118FB1007}"/>
+  <xr:revisionPtr revIDLastSave="580" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A07F6F91-0B9C-4684-837E-22892097675F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2271,6 +2271,32 @@
         <v>2066900</v>
       </c>
     </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A67" s="3">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" s="4">
+        <v>46209</v>
+      </c>
+      <c r="D67" s="21">
+        <v>36.6</v>
+      </c>
+      <c r="E67" s="21">
+        <v>36.9</v>
+      </c>
+      <c r="F67" s="21">
+        <v>34.15</v>
+      </c>
+      <c r="G67" s="21">
+        <v>35.1</v>
+      </c>
+      <c r="H67" s="19">
+        <v>3251400</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2280,7 +2306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2845,6 +2871,21 @@
         <v>39.011666666666663</v>
       </c>
     </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" s="11">
+        <v>37</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="15">
+        <v>46209</v>
+      </c>
+      <c r="D38" s="16">
+        <f>AVERAGE('Lịch sử giá'!G38:G67)</f>
+        <v>38.858333333333327</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="580" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A07F6F91-0B9C-4684-837E-22892097675F}"/>
+  <xr:revisionPtr revIDLastSave="588" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F33D67C4-E8C6-44C7-9837-870AFF9ADFDA}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2297,6 +2297,32 @@
         <v>3251400</v>
       </c>
     </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A68" s="3">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" s="4">
+        <v>46210</v>
+      </c>
+      <c r="D68" s="21">
+        <v>35.25</v>
+      </c>
+      <c r="E68" s="21">
+        <v>35.6</v>
+      </c>
+      <c r="F68" s="21">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="G68" s="21">
+        <v>34.9</v>
+      </c>
+      <c r="H68" s="19">
+        <v>2616200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2306,7 +2332,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2886,6 +2912,21 @@
         <v>38.858333333333327</v>
       </c>
     </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" s="11">
+        <v>38</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="15">
+        <v>46210</v>
+      </c>
+      <c r="D39" s="16">
+        <f>AVERAGE('Lịch sử giá'!G39:G68)</f>
+        <v>38.688333333333325</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="588" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F33D67C4-E8C6-44C7-9837-870AFF9ADFDA}"/>
+  <xr:revisionPtr revIDLastSave="596" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FF0B44E-A10B-4406-9A91-B7F04BB0E53B}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2323,6 +2323,32 @@
         <v>2616200</v>
       </c>
     </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A69" s="3">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69" s="4">
+        <v>46211</v>
+      </c>
+      <c r="D69" s="21">
+        <v>35.5</v>
+      </c>
+      <c r="E69" s="21">
+        <v>35.950000000000003</v>
+      </c>
+      <c r="F69" s="21">
+        <v>35.049999999999997</v>
+      </c>
+      <c r="G69" s="21">
+        <v>35.25</v>
+      </c>
+      <c r="H69" s="19">
+        <v>2210100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2332,7 +2358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2927,6 +2953,21 @@
         <v>38.688333333333325</v>
       </c>
     </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" s="11">
+        <v>39</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="15">
+        <v>46211</v>
+      </c>
+      <c r="D40" s="16">
+        <f>AVERAGE('Lịch sử giá'!G40:G69)</f>
+        <v>38.548333333333332</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="596" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FF0B44E-A10B-4406-9A91-B7F04BB0E53B}"/>
+  <xr:revisionPtr revIDLastSave="603" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85CFF630-F20B-4E82-A3E7-104FF427461D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2349,6 +2349,32 @@
         <v>2210100</v>
       </c>
     </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A70" s="3">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C70" s="4">
+        <v>46212</v>
+      </c>
+      <c r="D70" s="21">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="E70" s="21">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F70" s="21">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="G70" s="21">
+        <v>36</v>
+      </c>
+      <c r="H70" s="19">
+        <v>2889900</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2358,7 +2384,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -2968,6 +2994,21 @@
         <v>38.548333333333332</v>
       </c>
     </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" s="11">
+        <v>40</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="15">
+        <v>46212</v>
+      </c>
+      <c r="D41" s="16">
+        <f>AVERAGE('Lịch sử giá'!G41:G70)</f>
+        <v>38.43333333333333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="603" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85CFF630-F20B-4E82-A3E7-104FF427461D}"/>
+  <xr:revisionPtr revIDLastSave="611" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA559A54-5ADE-494E-9464-E9A97AC72AAB}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2375,6 +2375,32 @@
         <v>2889900</v>
       </c>
     </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A71" s="3">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="4">
+        <v>46213</v>
+      </c>
+      <c r="D71" s="21">
+        <v>36.6</v>
+      </c>
+      <c r="E71" s="21">
+        <v>36.950000000000003</v>
+      </c>
+      <c r="F71" s="21">
+        <v>36</v>
+      </c>
+      <c r="G71" s="21">
+        <v>36</v>
+      </c>
+      <c r="H71" s="19">
+        <v>2471800</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2384,7 +2410,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3009,6 +3035,21 @@
         <v>38.43333333333333</v>
       </c>
     </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" s="11">
+        <v>41</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="15">
+        <v>46213</v>
+      </c>
+      <c r="D42" s="16">
+        <f>AVERAGE('Lịch sử giá'!G42:G71)</f>
+        <v>38.266666666666673</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="611" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA559A54-5ADE-494E-9464-E9A97AC72AAB}"/>
+  <xr:revisionPtr revIDLastSave="621" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D7A0FD9-72DB-4E72-A295-3AC3269D8E11}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2401,6 +2401,32 @@
         <v>2471800</v>
       </c>
     </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A72" s="3">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" s="4">
+        <v>46216</v>
+      </c>
+      <c r="D72" s="21">
+        <v>36.5</v>
+      </c>
+      <c r="E72" s="21">
+        <v>36.549999999999997</v>
+      </c>
+      <c r="F72" s="21">
+        <v>35</v>
+      </c>
+      <c r="G72" s="21">
+        <v>35.549999999999997</v>
+      </c>
+      <c r="H72" s="19">
+        <v>1660600</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2410,7 +2436,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3050,6 +3076,21 @@
         <v>38.266666666666673</v>
       </c>
     </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" s="11">
+        <v>42</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="15">
+        <v>46216</v>
+      </c>
+      <c r="D43" s="16">
+        <f>AVERAGE('Lịch sử giá'!G43:G72)</f>
+        <v>38.126666666666665</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="621" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D7A0FD9-72DB-4E72-A295-3AC3269D8E11}"/>
+  <xr:revisionPtr revIDLastSave="633" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30891FE5-DDCD-4D12-A065-8669446E3809}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2427,6 +2427,32 @@
         <v>1660600</v>
       </c>
     </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A73" s="3">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C73" s="4">
+        <v>46217</v>
+      </c>
+      <c r="D73" s="21">
+        <v>36.15</v>
+      </c>
+      <c r="E73" s="21">
+        <v>37.35</v>
+      </c>
+      <c r="F73" s="21">
+        <v>35.549999999999997</v>
+      </c>
+      <c r="G73" s="21">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="H73" s="19">
+        <v>3602800</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2436,7 +2462,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3091,6 +3117,21 @@
         <v>38.126666666666665</v>
       </c>
     </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" s="11">
+        <v>43</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="15">
+        <v>46217</v>
+      </c>
+      <c r="D44" s="16">
+        <f>AVERAGE('Lịch sử giá'!G44:G73)</f>
+        <v>38.05833333333333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="633" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30891FE5-DDCD-4D12-A065-8669446E3809}"/>
+  <xr:revisionPtr revIDLastSave="641" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F15657B-B1B5-4E28-A330-97918161A808}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2453,6 +2453,32 @@
         <v>3602800</v>
       </c>
     </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A74" s="3">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" s="4">
+        <v>46218</v>
+      </c>
+      <c r="D74" s="21">
+        <v>36.950000000000003</v>
+      </c>
+      <c r="E74" s="21">
+        <v>36.950000000000003</v>
+      </c>
+      <c r="F74" s="21">
+        <v>36.049999999999997</v>
+      </c>
+      <c r="G74" s="21">
+        <v>36.049999999999997</v>
+      </c>
+      <c r="H74" s="19">
+        <v>1498800</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2462,7 +2488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3132,6 +3158,21 @@
         <v>38.05833333333333</v>
       </c>
     </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" s="11">
+        <v>44</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="15">
+        <v>46218</v>
+      </c>
+      <c r="D45" s="16">
+        <f>AVERAGE('Lịch sử giá'!G45:G74)</f>
+        <v>37.954999999999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="641" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F15657B-B1B5-4E28-A330-97918161A808}"/>
+  <xr:revisionPtr revIDLastSave="653" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D3B98B-0E91-44A1-948A-8F3A9AABF765}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2479,6 +2479,32 @@
         <v>1498800</v>
       </c>
     </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A75" s="3">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C75" s="4">
+        <v>46219</v>
+      </c>
+      <c r="D75" s="21">
+        <v>36.1</v>
+      </c>
+      <c r="E75" s="21">
+        <v>36.549999999999997</v>
+      </c>
+      <c r="F75" s="21">
+        <v>34.5</v>
+      </c>
+      <c r="G75" s="21">
+        <v>35.9</v>
+      </c>
+      <c r="H75" s="19">
+        <v>2072000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2488,7 +2514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3173,6 +3199,21 @@
         <v>37.954999999999998</v>
       </c>
     </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" s="11">
+        <v>45</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="15">
+        <v>46219</v>
+      </c>
+      <c r="D46" s="16">
+        <f>AVERAGE('Lịch sử giá'!G46:G75)</f>
+        <v>37.756666666666668</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="653" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D3B98B-0E91-44A1-948A-8F3A9AABF765}"/>
+  <xr:revisionPtr revIDLastSave="661" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7DDB1FD-D9BE-4B45-96B7-67B858B27637}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2505,6 +2505,32 @@
         <v>2072000</v>
       </c>
     </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A76" s="3">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" s="4">
+        <v>46220</v>
+      </c>
+      <c r="D76" s="21">
+        <v>35.9</v>
+      </c>
+      <c r="E76" s="21">
+        <v>36</v>
+      </c>
+      <c r="F76" s="21">
+        <v>35.1</v>
+      </c>
+      <c r="G76" s="21">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="H76" s="19">
+        <v>1001700</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2514,7 +2540,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3214,6 +3240,21 @@
         <v>37.756666666666668</v>
       </c>
     </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" s="11">
+        <v>46</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="15">
+        <v>46220</v>
+      </c>
+      <c r="D47" s="16">
+        <f>AVERAGE('Lịch sử giá'!G47:G76)</f>
+        <v>37.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="661" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7DDB1FD-D9BE-4B45-96B7-67B858B27637}"/>
+  <xr:revisionPtr revIDLastSave="671" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF4C3951-7358-4BEE-8A9C-914ED1D2096D}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -220,6 +220,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -539,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2531,6 +2535,32 @@
         <v>1001700</v>
       </c>
     </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A77" s="3">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="4">
+        <v>46223</v>
+      </c>
+      <c r="D77" s="21">
+        <v>35.549999999999997</v>
+      </c>
+      <c r="E77" s="21">
+        <v>35.85</v>
+      </c>
+      <c r="F77" s="21">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="G77" s="21">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="H77" s="19">
+        <v>1701400</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2540,7 +2570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3255,6 +3285,21 @@
         <v>37.53</v>
       </c>
     </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" s="11">
+        <v>47</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="15">
+        <v>46223</v>
+      </c>
+      <c r="D48" s="16">
+        <f>AVERAGE('Lịch sử giá'!G48:G77)</f>
+        <v>37.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="671" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF4C3951-7358-4BEE-8A9C-914ED1D2096D}"/>
+  <xr:revisionPtr revIDLastSave="672" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F91271E0-667F-4032-A15A-78B1EBDCE882}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử giá" sheetId="1" r:id="rId1"/>
@@ -220,10 +220,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2555,7 +2551,7 @@
         <v>34.299999999999997</v>
       </c>
       <c r="G77" s="21">
-        <v>34.200000000000003</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="H77" s="19">
         <v>1701400</v>
@@ -3297,7 +3293,7 @@
       </c>
       <c r="D48" s="16">
         <f>AVERAGE('Lịch sử giá'!G48:G77)</f>
-        <v>37.28</v>
+        <v>37.283333333333331</v>
       </c>
     </row>
   </sheetData>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="672" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F91271E0-667F-4032-A15A-78B1EBDCE882}"/>
+  <xr:revisionPtr revIDLastSave="680" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D45643E-9611-42EF-998B-A1CF4855A45E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2557,6 +2557,32 @@
         <v>1701400</v>
       </c>
     </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C78" s="4">
+        <v>46224</v>
+      </c>
+      <c r="D78" s="21">
+        <v>33.4</v>
+      </c>
+      <c r="E78" s="21">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="F78" s="21">
+        <v>31.9</v>
+      </c>
+      <c r="G78" s="21">
+        <v>32.65</v>
+      </c>
+      <c r="H78" s="19">
+        <v>3064500</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2566,7 +2592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3296,6 +3322,21 @@
         <v>37.283333333333331</v>
       </c>
     </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" s="11">
+        <v>48</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="15">
+        <v>46224</v>
+      </c>
+      <c r="D49" s="16">
+        <f>AVERAGE('Lịch sử giá'!G49:G78)</f>
+        <v>37.021666666666661</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="680" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D45643E-9611-42EF-998B-A1CF4855A45E}"/>
+  <xr:revisionPtr revIDLastSave="688" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23B54EC2-5366-491F-B702-D9F6DFDBBFFB}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2583,6 +2583,32 @@
         <v>3064500</v>
       </c>
     </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A79" s="3">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C79" s="4">
+        <v>46225</v>
+      </c>
+      <c r="D79" s="21">
+        <v>32.65</v>
+      </c>
+      <c r="E79" s="21">
+        <v>33.65</v>
+      </c>
+      <c r="F79" s="21">
+        <v>32.549999999999997</v>
+      </c>
+      <c r="G79" s="21">
+        <v>32.75</v>
+      </c>
+      <c r="H79" s="19">
+        <v>1759600</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2592,7 +2618,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3337,6 +3363,21 @@
         <v>37.021666666666661</v>
       </c>
     </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" s="11">
+        <v>49</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="15">
+        <v>46225</v>
+      </c>
+      <c r="D50" s="16">
+        <f>AVERAGE('Lịch sử giá'!G50:G79)</f>
+        <v>36.778333333333336</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="688" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23B54EC2-5366-491F-B702-D9F6DFDBBFFB}"/>
+  <xr:revisionPtr revIDLastSave="696" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F88EDFC3-937E-468E-B537-534ECDB1A405}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2609,6 +2609,32 @@
         <v>1759600</v>
       </c>
     </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A80" s="3">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C80" s="4">
+        <v>46226</v>
+      </c>
+      <c r="D80" s="21">
+        <v>33</v>
+      </c>
+      <c r="E80" s="21">
+        <v>33.6</v>
+      </c>
+      <c r="F80" s="21">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="G80" s="21">
+        <v>33.4</v>
+      </c>
+      <c r="H80" s="19">
+        <v>1465900</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2618,7 +2644,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3378,6 +3404,21 @@
         <v>36.778333333333336</v>
       </c>
     </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" s="11">
+        <v>50</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="15">
+        <v>46226</v>
+      </c>
+      <c r="D51" s="16">
+        <f>AVERAGE('Lịch sử giá'!G51:G80)</f>
+        <v>36.56333333333334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Du_lieu_PLX.xlsx
+++ b/Du_lieu_PLX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Cổ phiếu quỹ/PLX_web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="696" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F88EDFC3-937E-468E-B537-534ECDB1A405}"/>
+  <xr:revisionPtr revIDLastSave="706" documentId="13_ncr:1_{FBBB51D9-8AD3-4C6B-A21A-B98EDB197521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A16AA4B6-EC47-486C-B9B0-5A8B80BC5127}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="11">
   <si>
     <t>Mã</t>
   </si>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -2635,6 +2635,32 @@
         <v>1465900</v>
       </c>
     </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A81" s="3">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C81" s="4">
+        <v>46227</v>
+      </c>
+      <c r="D81" s="21">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="E81" s="21">
+        <v>34.450000000000003</v>
+      </c>
+      <c r="F81" s="21">
+        <v>33.75</v>
+      </c>
+      <c r="G81" s="21">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="H81" s="19">
+        <v>1713700</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2644,7 +2670,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22C0708-BF56-4452-AE72-2F555F429795}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.86328125" style="13"/>
@@ -3419,6 +3445,21 @@
         <v>36.56333333333334</v>
       </c>
     </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" s="11">
+        <v>51</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="15">
+        <v>46227</v>
+      </c>
+      <c r="D52" s="16">
+        <f>AVERAGE('Lịch sử giá'!G52:G81)</f>
+        <v>36.354999999999997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
